--- a/data/trans_orig/P1806_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1806_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses han visitado un podólogo en 2023</t>
+          <t>Población según si en los últimos 12 meses han visitado un podólogo en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21489</t>
+          <t>22329</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24021</t>
+          <t>23461</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33876</t>
+          <t>34548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>378498</t>
+          <t>377658</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398053</t>
+          <t>398066</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289179</t>
+          <t>289739</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>309074</t>
+          <t>308801</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>679311</t>
+          <t>678639</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>704789</t>
+          <t>704201</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>19992</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>19450</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9237</t>
+          <t>8840</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31939</t>
+          <t>29097</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403310</t>
+          <t>403555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421153</t>
+          <t>421064</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>492465</t>
+          <t>492054</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506916</t>
+          <t>507271</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>903112</t>
+          <t>905954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>925814</t>
+          <t>926211</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20049</t>
+          <t>20700</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>9741</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18994</t>
+          <t>18765</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37216</t>
+          <t>37399</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516289</t>
+          <t>515638</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>530740</t>
+          <t>530548</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>519352</t>
+          <t>520070</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>532534</t>
+          <t>532727</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1041590</t>
+          <t>1041407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1059812</t>
+          <t>1060041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20135</t>
+          <t>20549</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27900</t>
+          <t>27213</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46723</t>
+          <t>47107</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27533</t>
+          <t>25466</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62814</t>
+          <t>62329</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>867651</t>
+          <t>867237</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>884607</t>
+          <t>883836</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>666158</t>
+          <t>665774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>684981</t>
+          <t>685668</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1537853</t>
+          <t>1538338</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1573134</t>
+          <t>1575201</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17813</t>
+          <t>17457</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27210</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43300</t>
+          <t>43971</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34192</t>
+          <t>34968</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56014</t>
+          <t>56318</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>543421</t>
+          <t>543777</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>556252</t>
+          <t>556382</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>503927</t>
+          <t>503256</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>520017</t>
+          <t>520299</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1052446</t>
+          <t>1052142</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1074268</t>
+          <t>1073492</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>13653</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27749</t>
+          <t>27887</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10961</t>
+          <t>12906</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48935</t>
+          <t>49047</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26725</t>
+          <t>25951</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68436</t>
+          <t>68334</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>340416</t>
+          <t>340278</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>354224</t>
+          <t>354512</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>559433</t>
+          <t>559321</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>597407</t>
+          <t>595462</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>908097</t>
+          <t>908199</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>949808</t>
+          <t>950582</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8195</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19178</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33641</t>
+          <t>34030</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51030</t>
+          <t>51898</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45541</t>
+          <t>45855</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66878</t>
+          <t>66100</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>263581</t>
+          <t>264158</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>274382</t>
+          <t>274564</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>374235</t>
+          <t>373367</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>391624</t>
+          <t>391235</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>641146</t>
+          <t>641924</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>662483</t>
+          <t>662169</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>60157</t>
+          <t>58876</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102574</t>
+          <t>98977</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>145653</t>
+          <t>144518</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>205827</t>
+          <t>207013</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>223998</t>
+          <t>223470</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>295999</t>
+          <t>293469</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3357243</t>
+          <t>3360840</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3399660</t>
+          <t>3400941</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3455086</t>
+          <t>3453900</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3515260</t>
+          <t>3516395</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6824731</t>
+          <t>6827261</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6896732</t>
+          <t>6897260</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1806_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1806_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>18541</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>11028</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23461</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18148</t>
+          <t>17348</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34548</t>
+          <t>33568</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>392728</t>
+          <t>401474</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377658</t>
+          <t>389252</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398066</t>
+          <t>406305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>302311</t>
+          <t>351484</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289739</t>
+          <t>338402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308801</t>
+          <t>358436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>695039</t>
+          <t>752957</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>678639</t>
+          <t>736737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>704201</t>
+          <t>761932</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19992</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19450</t>
+          <t>19504</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>18343</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8840</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29097</t>
+          <t>32178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>415964</t>
+          <t>468856</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403555</t>
+          <t>455856</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421064</t>
+          <t>474486</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>490774</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>492054</t>
+          <t>481579</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>507271</t>
+          <t>496697</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>917183</t>
+          <t>959630</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>905954</t>
+          <t>945795</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926211</t>
+          <t>968535</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11496</t>
+          <t>11515</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20700</t>
+          <t>20344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15232</t>
+          <t>16935</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>10476</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>24786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>28450</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>20204</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37399</t>
+          <t>39292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>524842</t>
+          <t>609322</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>515638</t>
+          <t>600493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>530548</t>
+          <t>615123</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>527236</t>
+          <t>605204</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>520070</t>
+          <t>597353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>532727</t>
+          <t>611663</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1052078</t>
+          <t>1214526</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1041407</t>
+          <t>1203684</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1060041</t>
+          <t>1222772</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>11058</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20549</t>
+          <t>20013</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36444</t>
+          <t>40037</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27213</t>
+          <t>31405</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47107</t>
+          <t>50640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>47041</t>
+          <t>51095</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25466</t>
+          <t>41067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62329</t>
+          <t>64209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>877189</t>
+          <t>689559</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>867237</t>
+          <t>680604</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>883836</t>
+          <t>694986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>676437</t>
+          <t>696849</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>665774</t>
+          <t>686246</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>685668</t>
+          <t>705481</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1553626</t>
+          <t>1386409</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1538338</t>
+          <t>1373295</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1575201</t>
+          <t>1396437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17457</t>
+          <t>17549</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34591</t>
+          <t>37759</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>29691</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43971</t>
+          <t>47968</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>44340</t>
+          <t>47662</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34968</t>
+          <t>37051</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56318</t>
+          <t>59360</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>551486</t>
+          <t>599442</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>543777</t>
+          <t>591797</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>556382</t>
+          <t>604634</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>512636</t>
+          <t>570412</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>503256</t>
+          <t>560203</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>520299</t>
+          <t>578480</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1064120</t>
+          <t>1169855</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1052142</t>
+          <t>1158157</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1073492</t>
+          <t>1180466</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547227</t>
+          <t>608171</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547227</t>
+          <t>608171</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547227</t>
+          <t>608171</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1108460</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1108460</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1108460</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>21161</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13653</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27887</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29713</t>
+          <t>32865</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12906</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49047</t>
+          <t>42492</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>49709</t>
+          <t>54026</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25951</t>
+          <t>44230</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68334</t>
+          <t>67144</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>348169</t>
+          <t>385919</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>340278</t>
+          <t>376963</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>354512</t>
+          <t>392454</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>578655</t>
+          <t>406301</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>559321</t>
+          <t>396674</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>595462</t>
+          <t>413222</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>926824</t>
+          <t>792220</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>908199</t>
+          <t>779102</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>950582</t>
+          <t>802016</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>12947</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18601</t>
+          <t>21434</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42242</t>
+          <t>45204</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34030</t>
+          <t>36538</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51898</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>55189</t>
+          <t>59155</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45855</t>
+          <t>48259</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66100</t>
+          <t>71144</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>269812</t>
+          <t>296247</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>264158</t>
+          <t>288764</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>274564</t>
+          <t>300813</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>383023</t>
+          <t>418809</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>373367</t>
+          <t>408684</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>391235</t>
+          <t>427475</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>652835</t>
+          <t>715056</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>641924</t>
+          <t>703067</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>662169</t>
+          <t>725952</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>79627</t>
+          <t>81942</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58876</t>
+          <t>65067</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>98977</t>
+          <t>102269</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>179396</t>
+          <t>194137</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>144518</t>
+          <t>171546</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>207013</t>
+          <t>218572</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>259023</t>
+          <t>276079</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>223470</t>
+          <t>246892</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>293469</t>
+          <t>304186</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3380190</t>
+          <t>3450820</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3360840</t>
+          <t>3430493</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3400941</t>
+          <t>3467695</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3481517</t>
+          <t>3539833</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3453900</t>
+          <t>3515398</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3516395</t>
+          <t>3562424</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6861707</t>
+          <t>6990653</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6827261</t>
+          <t>6962546</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6897260</t>
+          <t>7019840</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
